--- a/docs/02_Graphical_Model.xlsx
+++ b/docs/02_Graphical_Model.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Danil\Desktop\Z_messenger\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAAECA0F-AD2C-476A-805F-BBB81AF73874}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9031AD50-3CCA-447C-8D49-9521A3CE9235}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -108,7 +108,7 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -390,221 +390,222 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:V11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.33203125" customWidth="1"/>
-    <col min="2" max="2" width="17.88671875" customWidth="1"/>
-    <col min="3" max="3" width="7.88671875" customWidth="1"/>
+    <col min="1" max="1" width="28.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="17.88671875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="7.88671875" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C1">
+      <c r="C1" s="1">
         <v>1</v>
       </c>
-      <c r="D1">
+      <c r="D1" s="1">
         <v>2</v>
       </c>
-      <c r="E1">
+      <c r="E1" s="1">
         <v>3</v>
       </c>
-      <c r="F1">
+      <c r="F1" s="1">
         <v>4</v>
       </c>
-      <c r="G1">
+      <c r="G1" s="1">
         <v>5</v>
       </c>
-      <c r="H1">
+      <c r="H1" s="1">
         <v>6</v>
       </c>
-      <c r="I1">
+      <c r="I1" s="1">
         <v>7</v>
       </c>
-      <c r="J1">
+      <c r="J1" s="1">
         <v>8</v>
       </c>
-      <c r="K1">
+      <c r="K1" s="1">
         <v>9</v>
       </c>
-      <c r="L1">
+      <c r="L1" s="1">
         <v>10</v>
       </c>
-      <c r="M1">
+      <c r="M1" s="1">
         <v>11</v>
       </c>
-      <c r="N1">
-        <v>12</v>
-      </c>
-      <c r="O1">
+      <c r="N1" s="1">
+        <v>12</v>
+      </c>
+      <c r="O1" s="1">
         <v>13</v>
       </c>
-      <c r="P1">
+      <c r="P1" s="1">
         <v>14</v>
       </c>
-      <c r="Q1">
+      <c r="Q1" s="1">
         <v>15</v>
       </c>
-      <c r="R1">
+      <c r="R1" s="1">
         <v>16</v>
       </c>
-      <c r="S1">
+      <c r="S1" s="1">
         <v>17</v>
       </c>
-      <c r="T1">
+      <c r="T1" s="1">
         <v>18</v>
       </c>
-      <c r="U1">
+      <c r="U1" s="1">
         <v>19</v>
       </c>
-      <c r="V1">
+      <c r="V1" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="1">
         <v>1</v>
       </c>
-      <c r="C2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="C2" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="1">
         <v>2</v>
       </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="C3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="1">
         <v>2</v>
       </c>
-      <c r="E4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="E4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="1">
         <v>2</v>
       </c>
-      <c r="G5" t="s">
-        <v>12</v>
-      </c>
-      <c r="H5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="G5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="2">
         <v>2</v>
       </c>
-      <c r="I6" t="s">
-        <v>12</v>
-      </c>
-      <c r="J6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="I6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="2">
         <v>1</v>
       </c>
-      <c r="K7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="K7" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="2">
         <v>5</v>
       </c>
-      <c r="L8" t="s">
-        <v>12</v>
-      </c>
-      <c r="M8" t="s">
-        <v>12</v>
-      </c>
-      <c r="N8" t="s">
-        <v>12</v>
-      </c>
-      <c r="O8" t="s">
-        <v>12</v>
-      </c>
-      <c r="P8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="L8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B9" s="2">
         <v>2</v>
       </c>
-      <c r="Q9" t="s">
-        <v>12</v>
-      </c>
-      <c r="R9" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="Q9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="R9" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="2">
         <v>3</v>
       </c>
-      <c r="S10" t="s">
-        <v>12</v>
-      </c>
-      <c r="T10" t="s">
-        <v>12</v>
-      </c>
-      <c r="U10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="S10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="T10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="U10" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B11" s="2">
         <v>1</v>
       </c>
-      <c r="U11" t="s">
+      <c r="U11" s="1" t="s">
         <v>12</v>
       </c>
     </row>
